--- a/data/raw/treasury_funds/cbr_budget_funds.xlsx
+++ b/data/raw/treasury_funds/cbr_budget_funds.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RukhlinaEY\AppData\Local\Temp\Rar$DIa23664.39923.rartemp\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RukhlinaEY\AppData\Local\Temp\Rar$DIa61496.34270.rartemp\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11535"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15765" windowHeight="5205"/>
   </bookViews>
   <sheets>
     <sheet name="в рублях" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="531" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="180">
   <si>
     <t>01.02.2012</t>
   </si>
@@ -534,6 +534,9 @@
   </si>
   <si>
     <t>01.04.2026</t>
+  </si>
+  <si>
+    <t>01.05.2026</t>
   </si>
   <si>
     <t>Остатки бюджетных средств на счетах, всего</t>
@@ -574,22 +577,30 @@
       <sz val="9"/>
       <color rgb="FF333333"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF333333"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color rgb="FF333333"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
     </font>
     <font>
       <sz val="20"/>
       <color rgb="FF333333"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
     </font>
   </fonts>
   <fills count="3">
@@ -939,16 +950,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:FP7"/>
+  <dimension ref="A1:FQ7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="49" customWidth="1"/>
-    <col min="2" max="172" width="16.5703125" customWidth="1"/>
+    <col min="2" max="173" width="16.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:172" s="1" customFormat="1" ht="81.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:173" s="1" customFormat="1" ht="81.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="7" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -962,7 +973,7 @@
       <c r="K1" s="7"/>
       <c r="L1" s="7"/>
     </row>
-    <row r="2" spans="1:172" s="1" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:173" s="1" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2"/>
       <c r="B2" s="3" t="s">
         <v>0</v>
@@ -1477,10 +1488,13 @@
       <c r="FP2" s="3" t="s">
         <v>170</v>
       </c>
+      <c r="FQ2" s="3" t="s">
+        <v>171</v>
+      </c>
     </row>
-    <row r="3" spans="1:172" s="1" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:173" s="1" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B3" s="5">
         <v>14914</v>
@@ -1995,10 +2009,13 @@
       <c r="FP3" s="5">
         <v>38659</v>
       </c>
+      <c r="FQ3" s="5">
+        <v>38758</v>
+      </c>
     </row>
-    <row r="4" spans="1:172" s="1" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:173" s="1" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B4" s="5">
         <v>1261</v>
@@ -2513,10 +2530,13 @@
       <c r="FP4" s="5">
         <v>2465</v>
       </c>
+      <c r="FQ4" s="5">
+        <v>3006</v>
+      </c>
     </row>
-    <row r="5" spans="1:172" s="1" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:173" s="1" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B5" s="5">
         <v>537</v>
@@ -3031,10 +3051,13 @@
       <c r="FP5" s="5">
         <v>35360</v>
       </c>
+      <c r="FQ5" s="5">
+        <v>34031</v>
+      </c>
     </row>
-    <row r="6" spans="1:172" s="1" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:173" s="1" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B6" s="5">
         <v>8546</v>
@@ -3549,10 +3572,13 @@
       <c r="FP6" s="5">
         <v>165</v>
       </c>
+      <c r="FQ6" s="5">
+        <v>157</v>
+      </c>
     </row>
-    <row r="7" spans="1:172" s="1" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:173" s="1" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B7" s="5">
         <v>4569</v>
@@ -4066,6 +4092,9 @@
       </c>
       <c r="FP7" s="5">
         <v>670</v>
+      </c>
+      <c r="FQ7" s="5">
+        <v>1564</v>
       </c>
     </row>
   </sheetData>
@@ -4080,16 +4109,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:FP7"/>
+  <dimension ref="A1:FQ7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="49" customWidth="1"/>
-    <col min="2" max="172" width="16.5703125" customWidth="1"/>
+    <col min="2" max="173" width="16.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:172" s="1" customFormat="1" ht="81.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:173" s="1" customFormat="1" ht="81.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="8" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -4103,7 +4132,7 @@
       <c r="K1" s="8"/>
       <c r="L1" s="8"/>
     </row>
-    <row r="2" spans="1:172" s="1" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:173" s="1" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2"/>
       <c r="B2" s="3" t="s">
         <v>0</v>
@@ -4618,10 +4647,13 @@
       <c r="FP2" s="3" t="s">
         <v>170</v>
       </c>
+      <c r="FQ2" s="3" t="s">
+        <v>171</v>
+      </c>
     </row>
-    <row r="3" spans="1:172" s="1" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:173" s="1" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B3" s="5">
         <v>34085</v>
@@ -5136,10 +5168,13 @@
       <c r="FP3" s="5">
         <v>53056</v>
       </c>
+      <c r="FQ3" s="5">
+        <v>55771</v>
+      </c>
     </row>
-    <row r="4" spans="1:172" s="1" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:173" s="1" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B4" s="5">
         <v>6854</v>
@@ -5654,10 +5689,13 @@
       <c r="FP4" s="5">
         <v>13353</v>
       </c>
+      <c r="FQ4" s="5">
+        <v>17907</v>
+      </c>
     </row>
-    <row r="5" spans="1:172" s="1" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:173" s="1" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B5" s="5">
         <v>2337</v>
@@ -6172,10 +6210,13 @@
       <c r="FP5" s="5">
         <v>0</v>
       </c>
+      <c r="FQ5" s="5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="6" spans="1:172" s="1" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:173" s="1" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B6" s="5">
         <v>24889</v>
@@ -6690,10 +6731,13 @@
       <c r="FP6" s="5">
         <v>39702</v>
       </c>
+      <c r="FQ6" s="5">
+        <v>37863</v>
+      </c>
     </row>
-    <row r="7" spans="1:172" s="1" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:173" s="1" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B7" s="5">
         <v>3</v>
@@ -7206,6 +7250,9 @@
         <v>0</v>
       </c>
       <c r="FP7" s="5">
+        <v>0</v>
+      </c>
+      <c r="FQ7" s="5">
         <v>0</v>
       </c>
     </row>
@@ -7221,16 +7268,16 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:FP7"/>
+  <dimension ref="A1:FQ7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="49" customWidth="1"/>
-    <col min="2" max="172" width="16.5703125" customWidth="1"/>
+    <col min="2" max="173" width="16.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:172" s="1" customFormat="1" ht="81.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:173" s="1" customFormat="1" ht="81.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="8" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -7244,7 +7291,7 @@
       <c r="K1" s="8"/>
       <c r="L1" s="8"/>
     </row>
-    <row r="2" spans="1:172" s="1" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:173" s="1" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2"/>
       <c r="B2" s="3" t="s">
         <v>0</v>
@@ -7759,10 +7806,13 @@
       <c r="FP2" s="3" t="s">
         <v>170</v>
       </c>
+      <c r="FQ2" s="3" t="s">
+        <v>171</v>
+      </c>
     </row>
-    <row r="3" spans="1:172" s="1" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:173" s="1" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B3" s="5">
         <v>48998</v>
@@ -8277,10 +8327,13 @@
       <c r="FP3" s="5">
         <v>91715</v>
       </c>
+      <c r="FQ3" s="5">
+        <v>94529</v>
+      </c>
     </row>
-    <row r="4" spans="1:172" s="1" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:173" s="1" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B4" s="5">
         <v>8116</v>
@@ -8795,10 +8848,13 @@
       <c r="FP4" s="5">
         <v>15818</v>
       </c>
+      <c r="FQ4" s="5">
+        <v>20914</v>
+      </c>
     </row>
-    <row r="5" spans="1:172" s="1" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:173" s="1" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B5" s="5">
         <v>2874</v>
@@ -9313,10 +9369,13 @@
       <c r="FP5" s="5">
         <v>35360</v>
       </c>
+      <c r="FQ5" s="5">
+        <v>34031</v>
+      </c>
     </row>
-    <row r="6" spans="1:172" s="1" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:173" s="1" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B6" s="5">
         <v>33435</v>
@@ -9831,10 +9890,13 @@
       <c r="FP6" s="5">
         <v>39867</v>
       </c>
+      <c r="FQ6" s="5">
+        <v>38020</v>
+      </c>
     </row>
-    <row r="7" spans="1:172" s="1" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:173" s="1" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B7" s="5">
         <v>4573</v>
@@ -10348,6 +10410,9 @@
       </c>
       <c r="FP7" s="5">
         <v>670</v>
+      </c>
+      <c r="FQ7" s="5">
+        <v>1564</v>
       </c>
     </row>
   </sheetData>
